--- a/prep_and_checklists/A24  /PREPLIST_A24  _03-12-2026_1.xlsx
+++ b/prep_and_checklists/A24  /PREPLIST_A24  _03-12-2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/A24  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0BA989-18B5-754D-8F4A-FFCECB345AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3618B425-D009-9A4E-BFBF-4A38E334D5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,7 +790,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,36 +818,51 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri (Body)"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri (Body)"/>
+      <u/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri (Body)"/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -907,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,18 +932,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1233,12 +1249,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.1640625" customWidth="1"/>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.83203125" customWidth="1"/>
+    <col min="4" max="4" width="65.33203125" customWidth="1"/>
     <col min="5" max="5" width="48.5" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" customWidth="1"/>
     <col min="7" max="7" width="55.6640625" customWidth="1"/>
@@ -1246,623 +1265,623 @@
     <col min="18" max="18" width="47.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="8"/>
+      <c r="D3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="8"/>
+      <c r="G3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="D4" s="8" t="s">
+      <c r="B4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="G4" s="8" t="s">
+      <c r="E4" s="8"/>
+      <c r="G4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="10" t="s">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="10" t="s">
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="10" t="s">
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="10" t="s">
+    <row r="24" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+    <row r="26" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="9" t="s">
+    <row r="27" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="10" t="s">
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="10" t="s">
+    <row r="31" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="11" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="10" t="s">
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G32" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="11" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="9" t="s">
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="10" t="s">
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G35" s="9" t="s">
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G35" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D36" s="9" t="s">
+    <row r="36" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="10" t="s">
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G38" s="10" t="s">
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G39" s="10" t="s">
+    <row r="39" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G39" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G40" s="10" t="s">
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G40" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G41" s="10" t="s">
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G42"/>
       <c r="H42"/>
     </row>
-    <row r="43" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G43"/>
       <c r="H43"/>
     </row>
-    <row r="44" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G44"/>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:8" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
       <c r="G45"/>
@@ -1877,9 +1896,9 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G4:H4"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="40" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -3000,5 +3019,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/prep_and_checklists/A24  /PREPLIST_A24  _03-12-2026_1.xlsx
+++ b/prep_and_checklists/A24  /PREPLIST_A24  _03-12-2026_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/A24  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3618B425-D009-9A4E-BFBF-4A38E334D5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A023CE9-AC01-AE4C-9781-1DC694EFA986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_sheet" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="262">
   <si>
     <t xml:space="preserve">A24  , Guests: 8   , 9:00 AM - 5:00 PM   ,Friday, March 20, 2026  </t>
   </si>
@@ -784,6 +784,42 @@
   </si>
   <si>
     <t>5lb green</t>
+  </si>
+  <si>
+    <t>Grilled Eggplant</t>
+  </si>
+  <si>
+    <t>focaccia</t>
+  </si>
+  <si>
+    <t>nut-free pesto</t>
+  </si>
+  <si>
+    <t>fresh mozzarella</t>
+  </si>
+  <si>
+    <t>arugula</t>
+  </si>
+  <si>
+    <t>grilled eggplant</t>
+  </si>
+  <si>
+    <t>roasted peppers</t>
+  </si>
+  <si>
+    <t>5 each</t>
+  </si>
+  <si>
+    <t>1 tub</t>
+  </si>
+  <si>
+    <t>2 x 1lb</t>
+  </si>
+  <si>
+    <t>4 each</t>
+  </si>
+  <si>
+    <t>1x can</t>
   </si>
 </sst>
 </file>
@@ -937,14 +973,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,614 +1312,657 @@
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="D3" s="7" t="s">
+      <c r="B3" s="10"/>
+      <c r="D3" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="G3" s="7" t="s">
+      <c r="E3" s="10"/>
+      <c r="G3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="8"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="10"/>
+      <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="G4" s="9" t="s">
+      <c r="E4" s="10"/>
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="8"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="8" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="8" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="8" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="8" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="8" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="8" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="8" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="8" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="8" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E35" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H27" s="11" t="s">
+      <c r="G35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="10" t="s">
+      <c r="G39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G40" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="G41" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G32" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D34" s="11" t="s">
+    </row>
+    <row r="42" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E42" s="8" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G35" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D36" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G38" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G39" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G40" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G41" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G42"/>
       <c r="H42"/>
     </row>
-    <row r="43" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45" spans="1:8" s="4" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
+      <c r="D45" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
